--- a/02_TRAVAIL/Lot1_Hostaway/MASTER_REF_HA_Listings.xlsx
+++ b/02_TRAVAIL/Lot1_Hostaway/MASTER_REF_HA_Listings.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -735,7 +735,11 @@
           <t>exported</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>exported</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>OUI</t>
@@ -743,7 +747,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -793,7 +797,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -843,7 +847,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -897,7 +901,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -947,7 +951,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -997,7 +1001,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1047,7 +1051,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1097,7 +1101,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1147,7 +1151,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1197,7 +1201,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1247,7 +1251,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1297,7 +1301,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1347,7 +1351,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:57+00:00</t>
+          <t>2026-08-17T05:24:50+00:00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
